--- a/credentials/Credentials_TKRO 3.xlsx
+++ b/credentials/Credentials_TKRO 3.xlsx
@@ -397,13 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +412,9 @@
       <c r="D1" t="str">
         <v>Password</v>
       </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -432,6 +429,9 @@
       <c r="D2" t="str">
         <v>123456</v>
       </c>
+      <c r="E2" t="str">
+        <v>oto20238031.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -446,6 +446,9 @@
       <c r="D3" t="str">
         <v>123456</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -460,6 +463,9 @@
       <c r="D4" t="str">
         <v>123456</v>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -474,6 +480,9 @@
       <c r="D5" t="str">
         <v>123456</v>
       </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -488,6 +497,9 @@
       <c r="D6" t="str">
         <v>123456</v>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -502,6 +514,9 @@
       <c r="D7" t="str">
         <v>123456</v>
       </c>
+      <c r="E7" t="str">
+        <v>oto20238046.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -516,6 +531,9 @@
       <c r="D8" t="str">
         <v>123456</v>
       </c>
+      <c r="E8" t="str">
+        <v>oto20238061.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -530,6 +548,9 @@
       <c r="D9" t="str">
         <v>123456</v>
       </c>
+      <c r="E9" t="str">
+        <v>oto20238066.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -544,6 +565,9 @@
       <c r="D10" t="str">
         <v>123456</v>
       </c>
+      <c r="E10" t="str">
+        <v>oto20238107.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -558,6 +582,9 @@
       <c r="D11" t="str">
         <v>123456</v>
       </c>
+      <c r="E11" t="str">
+        <v>oto20238115.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -572,6 +599,9 @@
       <c r="D12" t="str">
         <v>123456</v>
       </c>
+      <c r="E12" t="str">
+        <v>oto20238132.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -586,6 +616,9 @@
       <c r="D13" t="str">
         <v>123456</v>
       </c>
+      <c r="E13" t="str">
+        <v>oto20238138.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -600,6 +633,9 @@
       <c r="D14" t="str">
         <v>123456</v>
       </c>
+      <c r="E14" t="str">
+        <v>oto20238168.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -614,6 +650,9 @@
       <c r="D15" t="str">
         <v>123456</v>
       </c>
+      <c r="E15" t="str">
+        <v>oto20238192.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -628,6 +667,9 @@
       <c r="D16" t="str">
         <v>123456</v>
       </c>
+      <c r="E16" t="str">
+        <v>oto20238221.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -642,6 +684,9 @@
       <c r="D17" t="str">
         <v>123456</v>
       </c>
+      <c r="E17" t="str">
+        <v>oto20238236.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -656,6 +701,9 @@
       <c r="D18" t="str">
         <v>123456</v>
       </c>
+      <c r="E18" t="str">
+        <v>oto20238263.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -670,6 +718,9 @@
       <c r="D19" t="str">
         <v>123456</v>
       </c>
+      <c r="E19" t="str">
+        <v>oto20238271.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -684,6 +735,9 @@
       <c r="D20" t="str">
         <v>123456</v>
       </c>
+      <c r="E20" t="str">
+        <v>oto20238289.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -698,6 +752,9 @@
       <c r="D21" t="str">
         <v>123456</v>
       </c>
+      <c r="E21" t="str">
+        <v>oto20238331.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -712,6 +769,9 @@
       <c r="D22" t="str">
         <v>123456</v>
       </c>
+      <c r="E22" t="str">
+        <v>oto20238345.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -726,6 +786,9 @@
       <c r="D23" t="str">
         <v>123456</v>
       </c>
+      <c r="E23" t="str">
+        <v>oto20238364.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -740,6 +803,9 @@
       <c r="D24" t="str">
         <v>123456</v>
       </c>
+      <c r="E24" t="str">
+        <v>oto20238369.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -754,6 +820,9 @@
       <c r="D25" t="str">
         <v>123456</v>
       </c>
+      <c r="E25" t="str">
+        <v>oto20238378.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -768,6 +837,9 @@
       <c r="D26" t="str">
         <v>123456</v>
       </c>
+      <c r="E26" t="str">
+        <v>oto20238388.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -782,6 +854,9 @@
       <c r="D27" t="str">
         <v>123456</v>
       </c>
+      <c r="E27" t="str">
+        <v>oto20238397.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -796,6 +871,9 @@
       <c r="D28" t="str">
         <v>123456</v>
       </c>
+      <c r="E28" t="str">
+        <v>oto20238403.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -810,6 +888,9 @@
       <c r="D29" t="str">
         <v>123456</v>
       </c>
+      <c r="E29" t="str">
+        <v>oto20238407.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -824,6 +905,9 @@
       <c r="D30" t="str">
         <v>123456</v>
       </c>
+      <c r="E30" t="str">
+        <v>oto20238421.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -838,6 +922,9 @@
       <c r="D31" t="str">
         <v>123456</v>
       </c>
+      <c r="E31" t="str">
+        <v>oto20238436.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -852,6 +939,9 @@
       <c r="D32" t="str">
         <v>123456</v>
       </c>
+      <c r="E32" t="str">
+        <v>oto20238467.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -866,6 +956,9 @@
       <c r="D33" t="str">
         <v>123456</v>
       </c>
+      <c r="E33" t="str">
+        <v>oto20238476.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -880,6 +973,9 @@
       <c r="D34" t="str">
         <v>123456</v>
       </c>
+      <c r="E34" t="str">
+        <v>oto20238488.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -894,6 +990,9 @@
       <c r="D35" t="str">
         <v>123456</v>
       </c>
+      <c r="E35" t="str">
+        <v>oto20238502.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -908,6 +1007,9 @@
       <c r="D36" t="str">
         <v>123456</v>
       </c>
+      <c r="E36" t="str">
+        <v>oto20238516.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -922,6 +1024,9 @@
       <c r="D37" t="str">
         <v>123456</v>
       </c>
+      <c r="E37" t="str">
+        <v>oto20238528.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -936,6 +1041,9 @@
       <c r="D38" t="str">
         <v>123456</v>
       </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -950,6 +1058,9 @@
       <c r="D39" t="str">
         <v>123456</v>
       </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -964,6 +1075,9 @@
       <c r="D40" t="str">
         <v>123456</v>
       </c>
+      <c r="E40" t="str">
+        <v>oto20238584.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -978,10 +1092,13 @@
       <c r="D41" t="str">
         <v>123456</v>
       </c>
+      <c r="E41" t="str">
+        <v>oto20238619.siswa@smkn12malang.sch.id</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/credentials/Credentials_TKRO 3.xlsx
+++ b/credentials/Credentials_TKRO 3.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,670 +435,568 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" t="str">
-        <v>Admin 2 TKRO 3</v>
+        <v>AHMAD KEVIN ALISKI</v>
       </c>
       <c r="C3" t="str">
-        <v>admin2.tkro3</v>
+        <v>ahmad.kevin</v>
       </c>
       <c r="D3" t="str">
         <v>123456</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>oto20238046.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" t="str">
-        <v>Admin TKRO 3</v>
+        <v>ALDICO DWI PUTRANTO</v>
       </c>
       <c r="C4" t="str">
-        <v>admin.tkro3</v>
+        <v>aldico.dwi</v>
       </c>
       <c r="D4" t="str">
         <v>123456</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>oto20238061.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" t="str">
-        <v>Admin TKRO 3 1</v>
+        <v>ALDO MARSEL ADE RAMADHANI</v>
       </c>
       <c r="C5" t="str">
-        <v>admin.tkro3.1</v>
+        <v>aldo.marsel</v>
       </c>
       <c r="D5" t="str">
         <v>123456</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>oto20238066.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="str">
-        <v>Admin TKRO 3 2</v>
+        <v>ARDY HIDAYATULLOH</v>
       </c>
       <c r="C6" t="str">
-        <v>admin.tkro3.2</v>
+        <v>ardy.hidayatulloh</v>
       </c>
       <c r="D6" t="str">
         <v>123456</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>oto20238107.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="str">
-        <v>AHMAD KEVIN ALISKI</v>
+        <v>ARYA GUGAH WICAKSONO</v>
       </c>
       <c r="C7" t="str">
-        <v>ahmad.kevin</v>
+        <v>arya.gugah</v>
       </c>
       <c r="D7" t="str">
         <v>123456</v>
       </c>
       <c r="E7" t="str">
-        <v>oto20238046.siswa@smkn12malang.sch.id</v>
+        <v>oto20238115.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" t="str">
-        <v>ALDICO DWI PUTRANTO</v>
+        <v>BAYU FAIQ PRANATA</v>
       </c>
       <c r="C8" t="str">
-        <v>aldico.dwi</v>
+        <v>bayu.faiq</v>
       </c>
       <c r="D8" t="str">
         <v>123456</v>
       </c>
       <c r="E8" t="str">
-        <v>oto20238061.siswa@smkn12malang.sch.id</v>
+        <v>oto20238132.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" t="str">
-        <v>ALDO MARSEL ADE RAMADHANI</v>
+        <v>BINTANG BAGUS PRASETYO</v>
       </c>
       <c r="C9" t="str">
-        <v>aldo.marsel</v>
+        <v>bintang.bagus</v>
       </c>
       <c r="D9" t="str">
         <v>123456</v>
       </c>
       <c r="E9" t="str">
-        <v>oto20238066.siswa@smkn12malang.sch.id</v>
+        <v>oto20238138.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" t="str">
-        <v>ARDY HIDAYATULLOH</v>
+        <v>DARREL BAGUS PRIAMBODO</v>
       </c>
       <c r="C10" t="str">
-        <v>ardy.hidayatulloh</v>
+        <v>darrel.bagus</v>
       </c>
       <c r="D10" t="str">
         <v>123456</v>
       </c>
       <c r="E10" t="str">
-        <v>oto20238107.siswa@smkn12malang.sch.id</v>
+        <v>oto20238168.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" t="str">
-        <v>ARYA GUGAH WICAKSONO</v>
+        <v>DIDA FEBIAN FIONESTA</v>
       </c>
       <c r="C11" t="str">
-        <v>arya.gugah</v>
+        <v>dida.febian</v>
       </c>
       <c r="D11" t="str">
         <v>123456</v>
       </c>
       <c r="E11" t="str">
-        <v>oto20238115.siswa@smkn12malang.sch.id</v>
+        <v>oto20238192.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" t="str">
-        <v>BAYU FAIQ PRANATA</v>
+        <v>FACHRI RIUL GANGGA SUTIKNO</v>
       </c>
       <c r="C12" t="str">
-        <v>bayu.faiq</v>
+        <v>fachri.riul</v>
       </c>
       <c r="D12" t="str">
         <v>123456</v>
       </c>
       <c r="E12" t="str">
-        <v>oto20238132.siswa@smkn12malang.sch.id</v>
+        <v>oto20238221.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" t="str">
-        <v>BINTANG BAGUS PRASETYO</v>
+        <v>FEBRIAN EKA PRAMUDYA</v>
       </c>
       <c r="C13" t="str">
-        <v>bintang.bagus</v>
+        <v>febrian.eka</v>
       </c>
       <c r="D13" t="str">
         <v>123456</v>
       </c>
       <c r="E13" t="str">
-        <v>oto20238138.siswa@smkn12malang.sch.id</v>
+        <v>oto20238236.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="str">
-        <v>DARREL BAGUS PRIAMBODO</v>
+        <v>GALUNGGA ALIF CHUSUMA PUTRA</v>
       </c>
       <c r="C14" t="str">
-        <v>darrel.bagus</v>
+        <v>galungga.alif</v>
       </c>
       <c r="D14" t="str">
         <v>123456</v>
       </c>
       <c r="E14" t="str">
-        <v>oto20238168.siswa@smkn12malang.sch.id</v>
+        <v>oto20238263.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" t="str">
-        <v>DIDA FEBIAN FIONESTA</v>
+        <v>HABIB AL BAIHAQI NURIDA</v>
       </c>
       <c r="C15" t="str">
-        <v>dida.febian</v>
+        <v>habib.al</v>
       </c>
       <c r="D15" t="str">
         <v>123456</v>
       </c>
       <c r="E15" t="str">
-        <v>oto20238192.siswa@smkn12malang.sch.id</v>
+        <v>oto20238271.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B16" t="str">
-        <v>FACHRI RIUL GANGGA SUTIKNO</v>
+        <v>IQBAL IZZUDIN ISLAM</v>
       </c>
       <c r="C16" t="str">
-        <v>fachri.riul</v>
+        <v>iqbal.izzudin</v>
       </c>
       <c r="D16" t="str">
         <v>123456</v>
       </c>
       <c r="E16" t="str">
-        <v>oto20238221.siswa@smkn12malang.sch.id</v>
+        <v>oto20238289.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" t="str">
-        <v>FEBRIAN EKA PRAMUDYA</v>
+        <v>M DAMAR FAIS YUNURDIKA</v>
       </c>
       <c r="C17" t="str">
-        <v>febrian.eka</v>
+        <v>m.damar</v>
       </c>
       <c r="D17" t="str">
         <v>123456</v>
       </c>
       <c r="E17" t="str">
-        <v>oto20238236.siswa@smkn12malang.sch.id</v>
+        <v>oto20238331.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" t="str">
-        <v>GALUNGGA ALIF CHUSUMA PUTRA</v>
+        <v>MAULANA AHMAD MUSTOFA HILMY</v>
       </c>
       <c r="C18" t="str">
-        <v>galungga.alif</v>
+        <v>maulana.ahmad</v>
       </c>
       <c r="D18" t="str">
         <v>123456</v>
       </c>
       <c r="E18" t="str">
-        <v>oto20238263.siswa@smkn12malang.sch.id</v>
+        <v>oto20238345.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19" t="str">
-        <v>HABIB AL BAIHAQI NURIDA</v>
+        <v>MOCH ZIDANE DIMAS KUSUMA</v>
       </c>
       <c r="C19" t="str">
-        <v>habib.al</v>
+        <v>moch.zidane</v>
       </c>
       <c r="D19" t="str">
         <v>123456</v>
       </c>
       <c r="E19" t="str">
-        <v>oto20238271.siswa@smkn12malang.sch.id</v>
+        <v>oto20238364.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B20" t="str">
-        <v>IQBAL IZZUDIN ISLAM</v>
+        <v>MOCHAMAD FEBRIANSAH</v>
       </c>
       <c r="C20" t="str">
-        <v>iqbal.izzudin</v>
+        <v>mochamad.febriansah</v>
       </c>
       <c r="D20" t="str">
         <v>123456</v>
       </c>
       <c r="E20" t="str">
-        <v>oto20238289.siswa@smkn12malang.sch.id</v>
+        <v>oto20238369.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B21" t="str">
-        <v>M DAMAR FAIS YUNURDIKA</v>
+        <v>MOH FAISAL HIDAYAT</v>
       </c>
       <c r="C21" t="str">
-        <v>m.damar</v>
+        <v>moh.faisal</v>
       </c>
       <c r="D21" t="str">
         <v>123456</v>
       </c>
       <c r="E21" t="str">
-        <v>oto20238331.siswa@smkn12malang.sch.id</v>
+        <v>oto20238378.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B22" t="str">
-        <v>MAULANA AHMAD MUSTOFA HILMY</v>
+        <v>MUCHAMAD PANDU PRANATA</v>
       </c>
       <c r="C22" t="str">
-        <v>maulana.ahmad</v>
+        <v>muchamad.pandu</v>
       </c>
       <c r="D22" t="str">
         <v>123456</v>
       </c>
       <c r="E22" t="str">
-        <v>oto20238345.siswa@smkn12malang.sch.id</v>
+        <v>oto20238388.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B23" t="str">
-        <v>MOCH ZIDANE DIMAS KUSUMA</v>
+        <v>MUHAMMAD AIDIL FIKRI</v>
       </c>
       <c r="C23" t="str">
-        <v>moch.zidane</v>
+        <v>muhammad.aidil</v>
       </c>
       <c r="D23" t="str">
         <v>123456</v>
       </c>
       <c r="E23" t="str">
-        <v>oto20238364.siswa@smkn12malang.sch.id</v>
+        <v>oto20238397.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B24" t="str">
-        <v>MOCHAMAD FEBRIANSAH</v>
+        <v>MUHAMMAD ANDY IRAWAN</v>
       </c>
       <c r="C24" t="str">
-        <v>mochamad.febriansah</v>
+        <v>muhammad.andy</v>
       </c>
       <c r="D24" t="str">
         <v>123456</v>
       </c>
       <c r="E24" t="str">
-        <v>oto20238369.siswa@smkn12malang.sch.id</v>
+        <v>oto20238403.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B25" t="str">
-        <v>MOH FAISAL HIDAYAT</v>
+        <v>MUHAMMAD DAVID AL BUCHORI</v>
       </c>
       <c r="C25" t="str">
-        <v>moh.faisal</v>
+        <v>muhammad.david</v>
       </c>
       <c r="D25" t="str">
         <v>123456</v>
       </c>
       <c r="E25" t="str">
-        <v>oto20238378.siswa@smkn12malang.sch.id</v>
+        <v>oto20238407.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B26" t="str">
-        <v>MUCHAMAD PANDU PRANATA</v>
+        <v>MUHAMMAD ILHAM MUJAHIDIN</v>
       </c>
       <c r="C26" t="str">
-        <v>muchamad.pandu</v>
+        <v>muhammad.ilham</v>
       </c>
       <c r="D26" t="str">
         <v>123456</v>
       </c>
       <c r="E26" t="str">
-        <v>oto20238388.siswa@smkn12malang.sch.id</v>
+        <v>oto20238421.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B27" t="str">
-        <v>MUHAMMAD AIDIL FIKRI</v>
+        <v>MUHHAMAD RANDYKA PUTRA</v>
       </c>
       <c r="C27" t="str">
-        <v>muhammad.aidil</v>
+        <v>muhhamad.randyka</v>
       </c>
       <c r="D27" t="str">
         <v>123456</v>
       </c>
       <c r="E27" t="str">
-        <v>oto20238397.siswa@smkn12malang.sch.id</v>
+        <v>oto20238436.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B28" t="str">
-        <v>MUHAMMAD ANDY IRAWAN</v>
+        <v>NOVAN ARIYANTO SAPUTRA</v>
       </c>
       <c r="C28" t="str">
-        <v>muhammad.andy</v>
+        <v>novan.ariyanto</v>
       </c>
       <c r="D28" t="str">
         <v>123456</v>
       </c>
       <c r="E28" t="str">
-        <v>oto20238403.siswa@smkn12malang.sch.id</v>
+        <v>oto20238467.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B29" t="str">
-        <v>MUHAMMAD DAVID AL BUCHORI</v>
+        <v>PASHA CAHYA RAMADHAN</v>
       </c>
       <c r="C29" t="str">
-        <v>muhammad.david</v>
+        <v>pasha.cahya</v>
       </c>
       <c r="D29" t="str">
         <v>123456</v>
       </c>
       <c r="E29" t="str">
-        <v>oto20238407.siswa@smkn12malang.sch.id</v>
+        <v>oto20238476.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B30" t="str">
-        <v>MUHAMMAD ILHAM MUJAHIDIN</v>
+        <v>RACHMAN SYAIFUDIN</v>
       </c>
       <c r="C30" t="str">
-        <v>muhammad.ilham</v>
+        <v>rachman.syaifudin</v>
       </c>
       <c r="D30" t="str">
         <v>123456</v>
       </c>
       <c r="E30" t="str">
-        <v>oto20238421.siswa@smkn12malang.sch.id</v>
+        <v>oto20238488.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B31" t="str">
-        <v>MUHHAMAD RANDYKA PUTRA</v>
+        <v>RAMA SEVIAN LAUNANDA</v>
       </c>
       <c r="C31" t="str">
-        <v>muhhamad.randyka</v>
+        <v>rama.sevian</v>
       </c>
       <c r="D31" t="str">
         <v>123456</v>
       </c>
       <c r="E31" t="str">
-        <v>oto20238436.siswa@smkn12malang.sch.id</v>
+        <v>oto20238502.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B32" t="str">
-        <v>NOVAN ARIYANTO SAPUTRA</v>
+        <v>RENGGA NUR IKHLAS AWANSYACH</v>
       </c>
       <c r="C32" t="str">
-        <v>novan.ariyanto</v>
+        <v>rengga.nur</v>
       </c>
       <c r="D32" t="str">
         <v>123456</v>
       </c>
       <c r="E32" t="str">
-        <v>oto20238467.siswa@smkn12malang.sch.id</v>
+        <v>oto20238516.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B33" t="str">
-        <v>PASHA CAHYA RAMADHAN</v>
+        <v>REZA DAVA FERDIANSYAH</v>
       </c>
       <c r="C33" t="str">
-        <v>pasha.cahya</v>
+        <v>reza.dava</v>
       </c>
       <c r="D33" t="str">
         <v>123456</v>
       </c>
       <c r="E33" t="str">
-        <v>oto20238476.siswa@smkn12malang.sch.id</v>
+        <v>oto20238528.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B34" t="str">
-        <v>RACHMAN SYAIFUDIN</v>
+        <v>TIO ADI SYAHPUTRA</v>
       </c>
       <c r="C34" t="str">
-        <v>rachman.syaifudin</v>
+        <v>tio.adi</v>
       </c>
       <c r="D34" t="str">
         <v>123456</v>
       </c>
       <c r="E34" t="str">
-        <v>oto20238488.siswa@smkn12malang.sch.id</v>
+        <v>oto20238584.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B35" t="str">
-        <v>RAMA SEVIAN LAUNANDA</v>
+        <v>YUDHA AL AYUBI QADAFY</v>
       </c>
       <c r="C35" t="str">
-        <v>rama.sevian</v>
+        <v>yudha.al</v>
       </c>
       <c r="D35" t="str">
         <v>123456</v>
       </c>
       <c r="E35" t="str">
-        <v>oto20238502.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>RENGGA NUR IKHLAS AWANSYACH</v>
-      </c>
-      <c r="C36" t="str">
-        <v>rengga.nur</v>
-      </c>
-      <c r="D36" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E36" t="str">
-        <v>oto20238516.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>REZA DAVA FERDIANSYAH</v>
-      </c>
-      <c r="C37" t="str">
-        <v>reza.dava</v>
-      </c>
-      <c r="D37" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E37" t="str">
-        <v>oto20238528.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Siswa Biasa TKRO 3</v>
-      </c>
-      <c r="C38" t="str">
-        <v>siswa.tkro3</v>
-      </c>
-      <c r="D38" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Siswa TKRO 3</v>
-      </c>
-      <c r="C39" t="str">
-        <v>user.tkro3</v>
-      </c>
-      <c r="D39" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>TIO ADI SYAHPUTRA</v>
-      </c>
-      <c r="C40" t="str">
-        <v>tio.adi</v>
-      </c>
-      <c r="D40" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E40" t="str">
-        <v>oto20238584.siswa@smkn12malang.sch.id</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>YUDHA AL AYUBI QADAFY</v>
-      </c>
-      <c r="C41" t="str">
-        <v>yudha.al</v>
-      </c>
-      <c r="D41" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E41" t="str">
         <v>oto20238619.siswa@smkn12malang.sch.id</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E35"/>
   </ignoredErrors>
 </worksheet>
 </file>